--- a/output/xlsx/AdministradorEditaTerminal--GT-.xlsx
+++ b/output/xlsx/AdministradorEditaTerminal--GT-.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="61">
   <si>
     <t xml:space="preserve">System: </t>
   </si>
@@ -38,7 +38,7 @@
     <t>Reduced (Greedy Heuristic - Transition Coverage)</t>
   </si>
   <si>
-    <t>Size: 7 test case(s)</t>
+    <t>Size: 8 test case(s)</t>
   </si>
   <si>
     <t xml:space="preserve">Creation Date: </t>
@@ -171,6 +171,15 @@
   </si>
   <si>
     <t>TC7</t>
+  </si>
+  <si>
+    <t>Alternative Flow 6: Volta para tela inicial de sistema</t>
+  </si>
+  <si>
+    <t>Administrador: clica no botao Voltar</t>
+  </si>
+  <si>
+    <t>TC8</t>
   </si>
   <si>
     <t>Exception Flow 1: Usuario nao preenche algum campo obrigatorio</t>
@@ -277,7 +286,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F91"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="17.578125" customWidth="true" bestFit="true"/>
@@ -1251,13 +1260,13 @@
         <v>2.0</v>
       </c>
       <c r="B77" t="s" s="3">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="C77" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D77" t="s" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E77" t="s" s="3">
         <v>27</v>
@@ -1271,13 +1280,13 @@
         <v>3.0</v>
       </c>
       <c r="B78" t="s" s="3">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C78" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D78" t="s" s="3">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="E78" t="s" s="3">
         <v>27</v>
@@ -1291,13 +1300,13 @@
         <v>4.0</v>
       </c>
       <c r="B79" t="s" s="3">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="C79" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D79" t="s" s="3">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="E79" t="s" s="3">
         <v>27</v>
@@ -1311,7 +1320,148 @@
         <v>33</v>
       </c>
       <c r="B80" t="s" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="1">
+        <v>11</v>
+      </c>
+      <c r="B83" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="C83" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="E83" t="s" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="B84" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="E84" t="s" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="1">
+        <v>18</v>
+      </c>
+      <c r="B85" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="C86" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="D86" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="E86" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="F86" t="s" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B87" t="s" s="3">
+        <v>26</v>
+      </c>
+      <c r="C87" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D87" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="E87" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F87" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="B88" t="s" s="3">
+        <v>29</v>
+      </c>
+      <c r="C88" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D88" t="s" s="3">
+        <v>30</v>
+      </c>
+      <c r="E88" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F88" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="B89" t="s" s="3">
+        <v>31</v>
+      </c>
+      <c r="C89" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D89" t="s" s="3">
         <v>57</v>
+      </c>
+      <c r="E89" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F89" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="B90" t="s" s="3">
+        <v>58</v>
+      </c>
+      <c r="C90" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D90" t="s" s="3">
+        <v>59</v>
+      </c>
+      <c r="E90" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F90" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="B91" t="s" s="0">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/output/xlsx/AdministradorEditaTerminal--GT-.xlsx
+++ b/output/xlsx/AdministradorEditaTerminal--GT-.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="49">
   <si>
     <t xml:space="preserve">System: </t>
   </si>
@@ -38,7 +38,7 @@
     <t>Reduced (Greedy Heuristic - Transition Coverage)</t>
   </si>
   <si>
-    <t>Size: 8 test case(s)</t>
+    <t>Size: 4 test case(s)</t>
   </si>
   <si>
     <t xml:space="preserve">Creation Date: </t>
@@ -122,7 +122,7 @@
     <t>TC2</t>
   </si>
   <si>
-    <t>Alternative Flow 1: Ordena lista de Terminais</t>
+    <t>Alternative Flow 1: Usuario ordena lista de Terminais</t>
   </si>
   <si>
     <t>Administrador: ordena lista dos Terminais por alguma coluna</t>
@@ -131,7 +131,7 @@
     <t>TC3</t>
   </si>
   <si>
-    <t>Alternative Flow 2: Adiciona Beneficio associado a Terminal</t>
+    <t>Alternative Flow 2: Usuario adiciona Beneficio associado a Terminal</t>
   </si>
   <si>
     <t>Administrador: preenche os dados do novo beneficio e clica no botao 'Adicionar Benficio'</t>
@@ -146,46 +146,10 @@
     <t>TC4</t>
   </si>
   <si>
-    <t>Alternative Flow 3: Cancela edicao</t>
-  </si>
-  <si>
-    <t>Administrador: clica no botao de 'Cancelar'</t>
-  </si>
-  <si>
-    <t>TC5</t>
-  </si>
-  <si>
-    <t>Alternative Flow 4: Navega por paginas de tabela</t>
-  </si>
-  <si>
-    <t>Administrador: clica em botao de navegacao de paginas de tabela</t>
-  </si>
-  <si>
-    <t>TC6</t>
-  </si>
-  <si>
-    <t>Alternative Flow 5: Filtra lista de Terminais</t>
-  </si>
-  <si>
-    <t>Administrador: preenche campos de filtragem</t>
-  </si>
-  <si>
-    <t>TC7</t>
-  </si>
-  <si>
-    <t>Alternative Flow 6: Volta para tela inicial de sistema</t>
-  </si>
-  <si>
-    <t>Administrador: clica no botao Voltar</t>
-  </si>
-  <si>
-    <t>TC8</t>
-  </si>
-  <si>
     <t>Exception Flow 1: Usuario nao preenche algum campo obrigatorio</t>
   </si>
   <si>
-    <t>SYSTEM informa que o campo e obrigatorio</t>
+    <t>SYSTEM informa que o campo é obrigatorio</t>
   </si>
   <si>
     <t>Administrador: preenche o campo obrigatorio e clica no botao de 'Atualizar'</t>
@@ -286,7 +250,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F91"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="17.578125" customWidth="true" bestFit="true"/>
@@ -837,13 +801,13 @@
         <v>3.0</v>
       </c>
       <c r="B44" t="s" s="3">
+        <v>31</v>
+      </c>
+      <c r="C44" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D44" t="s" s="3">
         <v>45</v>
-      </c>
-      <c r="C44" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D44" t="s" s="3">
-        <v>28</v>
       </c>
       <c r="E44" t="s" s="3">
         <v>27</v>
@@ -857,13 +821,13 @@
         <v>4.0</v>
       </c>
       <c r="B45" t="s" s="3">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="C45" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D45" t="s" s="3">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="E45" t="s" s="3">
         <v>27</v>
@@ -873,595 +837,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="n" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="B46" t="s" s="3">
-        <v>31</v>
-      </c>
-      <c r="C46" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D46" t="s" s="3">
-        <v>32</v>
-      </c>
-      <c r="E46" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F46" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s" s="1">
+      <c r="A46" t="s" s="1">
         <v>33</v>
       </c>
-      <c r="B47" t="s" s="0">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s" s="1">
-        <v>11</v>
-      </c>
-      <c r="B50" t="s" s="0">
-        <v>46</v>
-      </c>
-      <c r="C50" t="s" s="1">
-        <v>13</v>
-      </c>
-      <c r="E50" t="s" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s" s="1">
-        <v>15</v>
-      </c>
-      <c r="B51" t="s" s="0">
-        <v>47</v>
-      </c>
-      <c r="E51" t="s" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s" s="1">
-        <v>18</v>
-      </c>
-      <c r="B52" t="s" s="0">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="C53" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="D53" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="E53" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="F53" t="s" s="2">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="B54" t="s" s="3">
-        <v>26</v>
-      </c>
-      <c r="C54" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D54" t="s" s="3">
-        <v>28</v>
-      </c>
-      <c r="E54" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F54" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="B55" t="s" s="3">
+      <c r="B46" t="s" s="0">
         <v>48</v>
-      </c>
-      <c r="C55" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D55" t="s" s="3">
-        <v>28</v>
-      </c>
-      <c r="E55" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F55" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="B56" t="s" s="3">
-        <v>29</v>
-      </c>
-      <c r="C56" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D56" t="s" s="3">
-        <v>30</v>
-      </c>
-      <c r="E56" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F56" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="B57" t="s" s="3">
-        <v>31</v>
-      </c>
-      <c r="C57" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D57" t="s" s="3">
-        <v>32</v>
-      </c>
-      <c r="E57" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F57" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s" s="1">
-        <v>33</v>
-      </c>
-      <c r="B58" t="s" s="0">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s" s="1">
-        <v>11</v>
-      </c>
-      <c r="B61" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="C61" t="s" s="1">
-        <v>13</v>
-      </c>
-      <c r="E61" t="s" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s" s="1">
-        <v>15</v>
-      </c>
-      <c r="B62" t="s" s="0">
-        <v>50</v>
-      </c>
-      <c r="E62" t="s" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s" s="1">
-        <v>18</v>
-      </c>
-      <c r="B63" t="s" s="0">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="C64" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="D64" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="E64" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="F64" t="s" s="2">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="B65" t="s" s="3">
-        <v>26</v>
-      </c>
-      <c r="C65" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D65" t="s" s="3">
-        <v>28</v>
-      </c>
-      <c r="E65" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F65" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="B66" t="s" s="3">
-        <v>51</v>
-      </c>
-      <c r="C66" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D66" t="s" s="3">
-        <v>28</v>
-      </c>
-      <c r="E66" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F66" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="B67" t="s" s="3">
-        <v>29</v>
-      </c>
-      <c r="C67" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D67" t="s" s="3">
-        <v>30</v>
-      </c>
-      <c r="E67" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F67" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="B68" t="s" s="3">
-        <v>31</v>
-      </c>
-      <c r="C68" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D68" t="s" s="3">
-        <v>32</v>
-      </c>
-      <c r="E68" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F68" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s" s="1">
-        <v>33</v>
-      </c>
-      <c r="B69" t="s" s="0">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s" s="1">
-        <v>11</v>
-      </c>
-      <c r="B72" t="s" s="0">
-        <v>52</v>
-      </c>
-      <c r="C72" t="s" s="1">
-        <v>13</v>
-      </c>
-      <c r="E72" t="s" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s" s="1">
-        <v>15</v>
-      </c>
-      <c r="B73" t="s" s="0">
-        <v>53</v>
-      </c>
-      <c r="E73" t="s" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s" s="1">
-        <v>18</v>
-      </c>
-      <c r="B74" t="s" s="0">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="C75" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="D75" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="E75" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="F75" t="s" s="2">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="B76" t="s" s="3">
-        <v>26</v>
-      </c>
-      <c r="C76" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D76" t="s" s="3">
-        <v>28</v>
-      </c>
-      <c r="E76" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F76" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="B77" t="s" s="3">
-        <v>54</v>
-      </c>
-      <c r="C77" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D77" t="s" s="3">
-        <v>28</v>
-      </c>
-      <c r="E77" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F77" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="B78" t="s" s="3">
-        <v>29</v>
-      </c>
-      <c r="C78" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D78" t="s" s="3">
-        <v>30</v>
-      </c>
-      <c r="E78" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F78" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="B79" t="s" s="3">
-        <v>31</v>
-      </c>
-      <c r="C79" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D79" t="s" s="3">
-        <v>32</v>
-      </c>
-      <c r="E79" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F79" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s" s="1">
-        <v>33</v>
-      </c>
-      <c r="B80" t="s" s="0">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s" s="1">
-        <v>11</v>
-      </c>
-      <c r="B83" t="s" s="0">
-        <v>55</v>
-      </c>
-      <c r="C83" t="s" s="1">
-        <v>13</v>
-      </c>
-      <c r="E83" t="s" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s" s="1">
-        <v>15</v>
-      </c>
-      <c r="B84" t="s" s="0">
-        <v>56</v>
-      </c>
-      <c r="E84" t="s" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s" s="1">
-        <v>18</v>
-      </c>
-      <c r="B85" t="s" s="0">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="B86" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="C86" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="D86" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="E86" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="F86" t="s" s="2">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="B87" t="s" s="3">
-        <v>26</v>
-      </c>
-      <c r="C87" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D87" t="s" s="3">
-        <v>28</v>
-      </c>
-      <c r="E87" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F87" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="n" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="B88" t="s" s="3">
-        <v>29</v>
-      </c>
-      <c r="C88" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D88" t="s" s="3">
-        <v>30</v>
-      </c>
-      <c r="E88" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F88" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="n" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="B89" t="s" s="3">
-        <v>31</v>
-      </c>
-      <c r="C89" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D89" t="s" s="3">
-        <v>57</v>
-      </c>
-      <c r="E89" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F89" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="B90" t="s" s="3">
-        <v>58</v>
-      </c>
-      <c r="C90" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D90" t="s" s="3">
-        <v>59</v>
-      </c>
-      <c r="E90" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F90" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s" s="1">
-        <v>33</v>
-      </c>
-      <c r="B91" t="s" s="0">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
